--- a/Data/EXCEL/Transfer/salemon/202206/6703-salemon-202206.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202206/6703-salemon-202206.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linea\OneDrive\myStocksPGMs\V2.0\xls2xlsx\transfer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORKSPACES\myStocksPGMs\V2.0\xls2xlsx\transfer\202206\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A53B70C-3034-4BA3-8B5B-223D5F22E97A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E604BC00-6903-4FE3-8DAB-875F5CD75D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="2625" windowWidth="24465" windowHeight="12855"/>
+    <workbookView xWindow="945" yWindow="3600" windowWidth="26925" windowHeight="11205"/>
   </bookViews>
   <sheets>
     <sheet name="6703-salemon-202206" sheetId="2" r:id="rId1"/>
@@ -1218,21 +1218,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q50"/>
+  <dimension ref="A1:Q51"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.125" customWidth="1"/>
-    <col min="2" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="10.5" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="10.5" customWidth="1"/>
-    <col min="10" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="10.5" customWidth="1"/>
-    <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="10.5" customWidth="1"/>
-    <col min="15" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="11.375" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="5" width="12.625" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="13.75" customWidth="1"/>
+    <col min="8" max="8" width="12.625" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="11" width="12.625" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="12.625" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="15" max="16" width="12.625" customWidth="1"/>
+    <col min="17" max="17" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1385,1120 +1385,1120 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B5" s="7">
-        <v>100.5</v>
+        <v>99.5</v>
       </c>
       <c r="C5" s="7">
-        <v>99</v>
+        <v>99.5</v>
       </c>
       <c r="D5" s="7">
-        <v>104.5</v>
+        <v>109.5</v>
       </c>
       <c r="E5" s="7">
-        <v>97.6</v>
+        <v>98</v>
       </c>
       <c r="F5" s="8">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="G5" s="8">
-        <v>0.1</v>
+        <v>0.51</v>
       </c>
       <c r="H5" s="9">
-        <v>1.51</v>
-      </c>
-      <c r="I5" s="8">
-        <v>16.7</v>
+        <v>1.29</v>
+      </c>
+      <c r="I5" s="10">
+        <v>-14.3</v>
       </c>
       <c r="J5" s="8">
-        <v>36.4</v>
+        <v>12.4</v>
       </c>
       <c r="K5" s="9">
-        <v>6</v>
+        <v>7.29</v>
       </c>
       <c r="L5" s="8">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="M5" s="9">
-        <v>1.51</v>
-      </c>
-      <c r="N5" s="8">
-        <v>16.7</v>
+        <v>1.29</v>
+      </c>
+      <c r="N5" s="10">
+        <v>-14.3</v>
       </c>
       <c r="O5" s="8">
-        <v>36.4</v>
+        <v>12.4</v>
       </c>
       <c r="P5" s="9">
-        <v>6</v>
+        <v>7.29</v>
       </c>
       <c r="Q5" s="8">
-        <v>13</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B6" s="7">
         <v>100.5</v>
       </c>
       <c r="C6" s="7">
-        <v>98.9</v>
+        <v>99</v>
       </c>
       <c r="D6" s="7">
-        <v>117</v>
+        <v>104.5</v>
       </c>
       <c r="E6" s="7">
-        <v>95</v>
-      </c>
-      <c r="F6" s="10">
-        <v>-0.2</v>
-      </c>
-      <c r="G6" s="10">
-        <v>-0.2</v>
+        <v>97.6</v>
+      </c>
+      <c r="F6" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="G6" s="8">
+        <v>0.1</v>
       </c>
       <c r="H6" s="9">
-        <v>1.29</v>
+        <v>1.51</v>
       </c>
       <c r="I6" s="8">
-        <v>2.2400000000000002</v>
+        <v>16.7</v>
       </c>
       <c r="J6" s="8">
-        <v>26.1</v>
+        <v>36.4</v>
       </c>
       <c r="K6" s="9">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="L6" s="8">
-        <v>6.87</v>
+        <v>13</v>
       </c>
       <c r="M6" s="9">
-        <v>1.29</v>
+        <v>1.51</v>
       </c>
       <c r="N6" s="8">
-        <v>2.2400000000000002</v>
+        <v>16.7</v>
       </c>
       <c r="O6" s="8">
-        <v>26.1</v>
+        <v>36.4</v>
       </c>
       <c r="P6" s="9">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="Q6" s="8">
-        <v>6.87</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B7" s="7">
-        <v>81.400000000000006</v>
+        <v>100.5</v>
       </c>
       <c r="C7" s="7">
-        <v>99.1</v>
+        <v>98.9</v>
       </c>
       <c r="D7" s="7">
-        <v>101.5</v>
+        <v>117</v>
       </c>
       <c r="E7" s="7">
-        <v>78.900000000000006</v>
-      </c>
-      <c r="F7" s="8">
-        <v>16.899999999999999</v>
-      </c>
-      <c r="G7" s="8">
-        <v>20.56</v>
+        <v>95</v>
+      </c>
+      <c r="F7" s="10">
+        <v>-0.2</v>
+      </c>
+      <c r="G7" s="10">
+        <v>-0.2</v>
       </c>
       <c r="H7" s="9">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="I7" s="8">
-        <v>21.1</v>
-      </c>
-      <c r="J7" s="10">
-        <v>-2.62</v>
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="J7" s="8">
+        <v>26.1</v>
       </c>
       <c r="K7" s="9">
-        <v>3.21</v>
+        <v>4.5</v>
       </c>
       <c r="L7" s="8">
-        <v>0.69</v>
+        <v>6.87</v>
       </c>
       <c r="M7" s="9">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="N7" s="8">
-        <v>21.1</v>
-      </c>
-      <c r="O7" s="10">
-        <v>-2.62</v>
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="O7" s="8">
+        <v>26.1</v>
       </c>
       <c r="P7" s="9">
-        <v>3.21</v>
+        <v>4.5</v>
       </c>
       <c r="Q7" s="8">
-        <v>0.69</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B8" s="7">
-        <v>84</v>
+        <v>81.400000000000006</v>
       </c>
       <c r="C8" s="7">
-        <v>82.2</v>
+        <v>99.1</v>
       </c>
       <c r="D8" s="7">
-        <v>84.9</v>
+        <v>101.5</v>
       </c>
       <c r="E8" s="7">
-        <v>81</v>
-      </c>
-      <c r="F8" s="10">
-        <v>-0.8</v>
-      </c>
-      <c r="G8" s="10">
-        <v>-0.96</v>
+        <v>78.900000000000006</v>
+      </c>
+      <c r="F8" s="8">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="G8" s="8">
+        <v>20.56</v>
       </c>
       <c r="H8" s="9">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="I8" s="8">
-        <v>15</v>
-      </c>
-      <c r="J8" s="8">
-        <v>5.95</v>
+        <v>21.1</v>
+      </c>
+      <c r="J8" s="10">
+        <v>-2.62</v>
       </c>
       <c r="K8" s="9">
-        <v>1.95</v>
+        <v>3.21</v>
       </c>
       <c r="L8" s="8">
-        <v>2.97</v>
+        <v>0.69</v>
       </c>
       <c r="M8" s="9">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="N8" s="8">
-        <v>15</v>
-      </c>
-      <c r="O8" s="8">
-        <v>5.95</v>
+        <v>21.1</v>
+      </c>
+      <c r="O8" s="10">
+        <v>-2.62</v>
       </c>
       <c r="P8" s="9">
-        <v>1.95</v>
+        <v>3.21</v>
       </c>
       <c r="Q8" s="8">
-        <v>2.97</v>
+        <v>0.69</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B9" s="7">
-        <v>85.2</v>
+        <v>84</v>
       </c>
       <c r="C9" s="7">
-        <v>83</v>
+        <v>82.2</v>
       </c>
       <c r="D9" s="7">
-        <v>86.2</v>
+        <v>84.9</v>
       </c>
       <c r="E9" s="7">
-        <v>82.5</v>
+        <v>81</v>
       </c>
       <c r="F9" s="10">
-        <v>-2.2000000000000002</v>
+        <v>-0.8</v>
       </c>
       <c r="G9" s="10">
-        <v>-2.58</v>
+        <v>-0.96</v>
       </c>
       <c r="H9" s="9">
-        <v>0.90600000000000003</v>
-      </c>
-      <c r="I9" s="10">
-        <v>-4.8899999999999997</v>
-      </c>
-      <c r="J9" s="10">
-        <v>-0.24</v>
+        <v>1.04</v>
+      </c>
+      <c r="I9" s="8">
+        <v>15</v>
+      </c>
+      <c r="J9" s="8">
+        <v>5.95</v>
       </c>
       <c r="K9" s="9">
-        <v>0.90600000000000003</v>
-      </c>
-      <c r="L9" s="10">
-        <v>-0.24</v>
+        <v>1.95</v>
+      </c>
+      <c r="L9" s="8">
+        <v>2.97</v>
       </c>
       <c r="M9" s="9">
-        <v>0.90600000000000003</v>
-      </c>
-      <c r="N9" s="10">
-        <v>-4.8899999999999997</v>
-      </c>
-      <c r="O9" s="10">
-        <v>-0.24</v>
+        <v>1.04</v>
+      </c>
+      <c r="N9" s="8">
+        <v>15</v>
+      </c>
+      <c r="O9" s="8">
+        <v>5.95</v>
       </c>
       <c r="P9" s="9">
-        <v>0.90600000000000003</v>
-      </c>
-      <c r="Q9" s="10">
-        <v>-0.24</v>
+        <v>1.95</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>2.97</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B10" s="7">
-        <v>88.8</v>
+        <v>85.2</v>
       </c>
       <c r="C10" s="7">
-        <v>85.2</v>
+        <v>83</v>
       </c>
       <c r="D10" s="7">
-        <v>88.8</v>
+        <v>86.2</v>
       </c>
       <c r="E10" s="7">
-        <v>84.1</v>
+        <v>82.5</v>
       </c>
       <c r="F10" s="10">
-        <v>-1.7</v>
+        <v>-2.2000000000000002</v>
       </c>
       <c r="G10" s="10">
-        <v>-1.96</v>
+        <v>-2.58</v>
       </c>
       <c r="H10" s="9">
-        <v>0.95199999999999996</v>
+        <v>0.90600000000000003</v>
       </c>
       <c r="I10" s="10">
-        <v>-46.7</v>
-      </c>
-      <c r="J10" s="8">
-        <v>6.59</v>
+        <v>-4.8899999999999997</v>
+      </c>
+      <c r="J10" s="10">
+        <v>-0.24</v>
       </c>
       <c r="K10" s="9">
-        <v>13.56</v>
-      </c>
-      <c r="L10" s="8">
-        <v>2</v>
+        <v>0.90600000000000003</v>
+      </c>
+      <c r="L10" s="10">
+        <v>-0.24</v>
       </c>
       <c r="M10" s="9">
-        <v>0.95199999999999996</v>
+        <v>0.90600000000000003</v>
       </c>
       <c r="N10" s="10">
-        <v>-46.7</v>
-      </c>
-      <c r="O10" s="8">
-        <v>6.59</v>
+        <v>-4.8899999999999997</v>
+      </c>
+      <c r="O10" s="10">
+        <v>-0.24</v>
       </c>
       <c r="P10" s="9">
-        <v>13.56</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>2</v>
+        <v>0.90600000000000003</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>-0.24</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B11" s="7">
-        <v>86.8</v>
+        <v>88.8</v>
       </c>
       <c r="C11" s="7">
-        <v>86.9</v>
+        <v>85.2</v>
       </c>
       <c r="D11" s="7">
-        <v>92.3</v>
+        <v>88.8</v>
       </c>
       <c r="E11" s="7">
-        <v>84.8</v>
-      </c>
-      <c r="F11" s="9">
-        <v>0</v>
-      </c>
-      <c r="G11" s="9">
-        <v>0</v>
+        <v>84.1</v>
+      </c>
+      <c r="F11" s="10">
+        <v>-1.7</v>
+      </c>
+      <c r="G11" s="10">
+        <v>-1.96</v>
       </c>
       <c r="H11" s="9">
-        <v>1.79</v>
-      </c>
-      <c r="I11" s="8">
-        <v>46.4</v>
-      </c>
-      <c r="J11" s="10">
-        <v>-10.7</v>
+        <v>0.95199999999999996</v>
+      </c>
+      <c r="I11" s="10">
+        <v>-46.7</v>
+      </c>
+      <c r="J11" s="8">
+        <v>6.59</v>
       </c>
       <c r="K11" s="9">
-        <v>12.6</v>
+        <v>13.56</v>
       </c>
       <c r="L11" s="8">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="M11" s="9">
-        <v>1.79</v>
-      </c>
-      <c r="N11" s="8">
-        <v>46.4</v>
-      </c>
-      <c r="O11" s="10">
-        <v>-10.7</v>
+        <v>0.95199999999999996</v>
+      </c>
+      <c r="N11" s="10">
+        <v>-46.7</v>
+      </c>
+      <c r="O11" s="8">
+        <v>6.59</v>
       </c>
       <c r="P11" s="9">
-        <v>12.6</v>
+        <v>13.56</v>
       </c>
       <c r="Q11" s="8">
-        <v>1.67</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B12" s="7">
-        <v>84</v>
+        <v>86.8</v>
       </c>
       <c r="C12" s="7">
         <v>86.9</v>
       </c>
       <c r="D12" s="7">
-        <v>88.9</v>
+        <v>92.3</v>
       </c>
       <c r="E12" s="7">
-        <v>82.6</v>
-      </c>
-      <c r="F12" s="8">
-        <v>1.9</v>
-      </c>
-      <c r="G12" s="8">
-        <v>2.2400000000000002</v>
+        <v>84.8</v>
+      </c>
+      <c r="F12" s="9">
+        <v>0</v>
+      </c>
+      <c r="G12" s="9">
+        <v>0</v>
       </c>
       <c r="H12" s="9">
-        <v>1.22</v>
-      </c>
-      <c r="I12" s="10">
-        <v>-0.65</v>
-      </c>
-      <c r="J12" s="8">
-        <v>12.1</v>
+        <v>1.79</v>
+      </c>
+      <c r="I12" s="8">
+        <v>46.4</v>
+      </c>
+      <c r="J12" s="10">
+        <v>-10.7</v>
       </c>
       <c r="K12" s="9">
-        <v>10.82</v>
+        <v>12.6</v>
       </c>
       <c r="L12" s="8">
-        <v>4.0599999999999996</v>
+        <v>1.67</v>
       </c>
       <c r="M12" s="9">
-        <v>1.22</v>
-      </c>
-      <c r="N12" s="10">
-        <v>-0.65</v>
-      </c>
-      <c r="O12" s="8">
-        <v>12.1</v>
+        <v>1.79</v>
+      </c>
+      <c r="N12" s="8">
+        <v>46.4</v>
+      </c>
+      <c r="O12" s="10">
+        <v>-10.7</v>
       </c>
       <c r="P12" s="9">
-        <v>10.82</v>
+        <v>12.6</v>
       </c>
       <c r="Q12" s="8">
-        <v>4.0599999999999996</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B13" s="7">
-        <v>91.7</v>
+        <v>84</v>
       </c>
       <c r="C13" s="7">
-        <v>85</v>
+        <v>86.9</v>
       </c>
       <c r="D13" s="7">
-        <v>91.7</v>
+        <v>88.9</v>
       </c>
       <c r="E13" s="7">
-        <v>82</v>
-      </c>
-      <c r="F13" s="10">
-        <v>-6.3</v>
-      </c>
-      <c r="G13" s="10">
-        <v>-6.9</v>
+        <v>82.6</v>
+      </c>
+      <c r="F13" s="8">
+        <v>1.9</v>
+      </c>
+      <c r="G13" s="8">
+        <v>2.2400000000000002</v>
       </c>
       <c r="H13" s="9">
-        <v>1.23</v>
-      </c>
-      <c r="I13" s="8">
-        <v>33.799999999999997</v>
+        <v>1.22</v>
+      </c>
+      <c r="I13" s="10">
+        <v>-0.65</v>
       </c>
       <c r="J13" s="8">
-        <v>4.82</v>
+        <v>12.1</v>
       </c>
       <c r="K13" s="9">
-        <v>9.6</v>
+        <v>10.82</v>
       </c>
       <c r="L13" s="8">
-        <v>3.11</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="M13" s="9">
-        <v>1.23</v>
-      </c>
-      <c r="N13" s="8">
-        <v>33.799999999999997</v>
+        <v>1.22</v>
+      </c>
+      <c r="N13" s="10">
+        <v>-0.65</v>
       </c>
       <c r="O13" s="8">
-        <v>4.82</v>
+        <v>12.1</v>
       </c>
       <c r="P13" s="9">
-        <v>9.6</v>
+        <v>10.82</v>
       </c>
       <c r="Q13" s="8">
-        <v>3.11</v>
+        <v>4.0599999999999996</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B14" s="7">
-        <v>96.5</v>
+        <v>91.7</v>
       </c>
       <c r="C14" s="7">
-        <v>91.3</v>
+        <v>85</v>
       </c>
       <c r="D14" s="7">
-        <v>97.5</v>
+        <v>91.7</v>
       </c>
       <c r="E14" s="7">
-        <v>81.2</v>
+        <v>82</v>
       </c>
       <c r="F14" s="10">
-        <v>-5.5</v>
+        <v>-6.3</v>
       </c>
       <c r="G14" s="10">
-        <v>-5.68</v>
+        <v>-6.9</v>
       </c>
       <c r="H14" s="9">
-        <v>0.91800000000000004</v>
-      </c>
-      <c r="I14" s="10">
-        <v>-7.08</v>
-      </c>
-      <c r="J14" s="10">
-        <v>-18.7</v>
+        <v>1.23</v>
+      </c>
+      <c r="I14" s="8">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="J14" s="8">
+        <v>4.82</v>
       </c>
       <c r="K14" s="9">
-        <v>8.3699999999999992</v>
+        <v>9.6</v>
       </c>
       <c r="L14" s="8">
-        <v>2.87</v>
+        <v>3.11</v>
       </c>
       <c r="M14" s="9">
-        <v>0.91800000000000004</v>
-      </c>
-      <c r="N14" s="10">
-        <v>-7.08</v>
-      </c>
-      <c r="O14" s="10">
-        <v>-18.7</v>
+        <v>1.23</v>
+      </c>
+      <c r="N14" s="8">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="O14" s="8">
+        <v>4.82</v>
       </c>
       <c r="P14" s="9">
-        <v>8.3699999999999992</v>
+        <v>9.6</v>
       </c>
       <c r="Q14" s="8">
-        <v>2.87</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B15" s="7">
-        <v>98.8</v>
+        <v>96.5</v>
       </c>
       <c r="C15" s="7">
-        <v>96.8</v>
+        <v>91.3</v>
       </c>
       <c r="D15" s="7">
-        <v>106</v>
+        <v>97.5</v>
       </c>
       <c r="E15" s="7">
-        <v>95.8</v>
+        <v>81.2</v>
       </c>
       <c r="F15" s="10">
-        <v>-2.2000000000000002</v>
+        <v>-5.5</v>
       </c>
       <c r="G15" s="10">
-        <v>-2.2200000000000002</v>
+        <v>-5.68</v>
       </c>
       <c r="H15" s="9">
-        <v>0.98799999999999999</v>
+        <v>0.91800000000000004</v>
       </c>
       <c r="I15" s="10">
-        <v>-13.9</v>
+        <v>-7.08</v>
       </c>
       <c r="J15" s="10">
-        <v>-13.2</v>
+        <v>-18.7</v>
       </c>
       <c r="K15" s="9">
-        <v>7.45</v>
+        <v>8.3699999999999992</v>
       </c>
       <c r="L15" s="8">
-        <v>6.34</v>
+        <v>2.87</v>
       </c>
       <c r="M15" s="9">
-        <v>0.98799999999999999</v>
+        <v>0.91800000000000004</v>
       </c>
       <c r="N15" s="10">
-        <v>-13.9</v>
+        <v>-7.08</v>
       </c>
       <c r="O15" s="10">
-        <v>-13.2</v>
+        <v>-18.7</v>
       </c>
       <c r="P15" s="9">
-        <v>7.45</v>
+        <v>8.3699999999999992</v>
       </c>
       <c r="Q15" s="8">
-        <v>6.34</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B16" s="7">
-        <v>99.5</v>
+        <v>98.8</v>
       </c>
       <c r="C16" s="7">
-        <v>99</v>
+        <v>96.8</v>
       </c>
       <c r="D16" s="7">
-        <v>100.5</v>
+        <v>106</v>
       </c>
       <c r="E16" s="7">
-        <v>96.6</v>
+        <v>95.8</v>
       </c>
       <c r="F16" s="10">
-        <v>-0.5</v>
+        <v>-2.2000000000000002</v>
       </c>
       <c r="G16" s="10">
-        <v>-0.5</v>
+        <v>-2.2200000000000002</v>
       </c>
       <c r="H16" s="9">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="I16" s="8">
-        <v>4</v>
+        <v>0.98799999999999999</v>
+      </c>
+      <c r="I16" s="10">
+        <v>-13.9</v>
       </c>
       <c r="J16" s="10">
-        <v>-5.0199999999999996</v>
+        <v>-13.2</v>
       </c>
       <c r="K16" s="9">
-        <v>6.46</v>
+        <v>7.45</v>
       </c>
       <c r="L16" s="8">
-        <v>10.1</v>
+        <v>6.34</v>
       </c>
       <c r="M16" s="9">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="N16" s="8">
-        <v>4</v>
+        <v>0.98799999999999999</v>
+      </c>
+      <c r="N16" s="10">
+        <v>-13.9</v>
       </c>
       <c r="O16" s="10">
-        <v>-5.0199999999999996</v>
+        <v>-13.2</v>
       </c>
       <c r="P16" s="9">
-        <v>6.46</v>
+        <v>7.45</v>
       </c>
       <c r="Q16" s="8">
-        <v>10.1</v>
+        <v>6.34</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B17" s="7">
-        <v>111</v>
+        <v>99.5</v>
       </c>
       <c r="C17" s="7">
-        <v>99.5</v>
+        <v>99</v>
       </c>
       <c r="D17" s="7">
-        <v>111.5</v>
+        <v>100.5</v>
       </c>
       <c r="E17" s="7">
-        <v>93.5</v>
+        <v>96.6</v>
       </c>
       <c r="F17" s="10">
-        <v>-11.5</v>
+        <v>-0.5</v>
       </c>
       <c r="G17" s="10">
-        <v>-10.36</v>
+        <v>-0.5</v>
       </c>
       <c r="H17" s="9">
-        <v>1.1000000000000001</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="I17" s="8">
-        <v>7.89</v>
-      </c>
-      <c r="J17" s="8">
-        <v>2.98</v>
+        <v>4</v>
+      </c>
+      <c r="J17" s="10">
+        <v>-5.0199999999999996</v>
       </c>
       <c r="K17" s="9">
-        <v>5.31</v>
+        <v>6.46</v>
       </c>
       <c r="L17" s="8">
-        <v>14.1</v>
+        <v>10.1</v>
       </c>
       <c r="M17" s="9">
-        <v>1.1000000000000001</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="N17" s="8">
-        <v>7.89</v>
-      </c>
-      <c r="O17" s="8">
-        <v>2.98</v>
+        <v>4</v>
+      </c>
+      <c r="O17" s="10">
+        <v>-5.0199999999999996</v>
       </c>
       <c r="P17" s="9">
-        <v>5.31</v>
+        <v>6.46</v>
       </c>
       <c r="Q17" s="8">
-        <v>14.1</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B18" s="7">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C18" s="7">
-        <v>111</v>
+        <v>99.5</v>
       </c>
       <c r="D18" s="7">
-        <v>118</v>
+        <v>111.5</v>
       </c>
       <c r="E18" s="7">
-        <v>108.5</v>
+        <v>93.5</v>
       </c>
       <c r="F18" s="10">
-        <v>-0.5</v>
+        <v>-11.5</v>
       </c>
       <c r="G18" s="10">
-        <v>-0.45</v>
+        <v>-10.36</v>
       </c>
       <c r="H18" s="9">
-        <v>1.02</v>
-      </c>
-      <c r="I18" s="10">
-        <v>-21</v>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="I18" s="8">
+        <v>7.89</v>
       </c>
       <c r="J18" s="8">
-        <v>0.71</v>
+        <v>2.98</v>
       </c>
       <c r="K18" s="9">
-        <v>4.21</v>
+        <v>5.31</v>
       </c>
       <c r="L18" s="8">
-        <v>17.399999999999999</v>
+        <v>14.1</v>
       </c>
       <c r="M18" s="9">
-        <v>1.02</v>
-      </c>
-      <c r="N18" s="10">
-        <v>-21</v>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="N18" s="8">
+        <v>7.89</v>
       </c>
       <c r="O18" s="8">
-        <v>0.71</v>
+        <v>2.98</v>
       </c>
       <c r="P18" s="9">
-        <v>4.21</v>
+        <v>5.31</v>
       </c>
       <c r="Q18" s="8">
-        <v>17.399999999999999</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B19" s="7">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C19" s="7">
-        <v>111.5</v>
+        <v>111</v>
       </c>
       <c r="D19" s="7">
-        <v>115.5</v>
+        <v>118</v>
       </c>
       <c r="E19" s="7">
-        <v>106</v>
-      </c>
-      <c r="F19" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="G19" s="8">
-        <v>1.36</v>
+        <v>108.5</v>
+      </c>
+      <c r="F19" s="10">
+        <v>-0.5</v>
+      </c>
+      <c r="G19" s="10">
+        <v>-0.45</v>
       </c>
       <c r="H19" s="9">
-        <v>1.3</v>
-      </c>
-      <c r="I19" s="8">
-        <v>31.8</v>
+        <v>1.02</v>
+      </c>
+      <c r="I19" s="10">
+        <v>-21</v>
       </c>
       <c r="J19" s="8">
-        <v>52.5</v>
+        <v>0.71</v>
       </c>
       <c r="K19" s="9">
-        <v>3.19</v>
+        <v>4.21</v>
       </c>
       <c r="L19" s="8">
-        <v>24</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="M19" s="9">
-        <v>1.3</v>
-      </c>
-      <c r="N19" s="8">
-        <v>31.8</v>
+        <v>1.02</v>
+      </c>
+      <c r="N19" s="10">
+        <v>-21</v>
       </c>
       <c r="O19" s="8">
-        <v>52.5</v>
+        <v>0.71</v>
       </c>
       <c r="P19" s="9">
-        <v>3.19</v>
+        <v>4.21</v>
       </c>
       <c r="Q19" s="8">
-        <v>24</v>
+        <v>17.399999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B20" s="7">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C20" s="7">
-        <v>110</v>
+        <v>111.5</v>
       </c>
       <c r="D20" s="7">
-        <v>117</v>
+        <v>115.5</v>
       </c>
       <c r="E20" s="7">
         <v>106</v>
       </c>
       <c r="F20" s="8">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="G20" s="8">
-        <v>3.29</v>
+        <v>1.36</v>
       </c>
       <c r="H20" s="9">
-        <v>0.98299999999999998</v>
+        <v>1.3</v>
       </c>
       <c r="I20" s="8">
-        <v>8.25</v>
+        <v>31.8</v>
       </c>
       <c r="J20" s="8">
-        <v>29.4</v>
+        <v>52.5</v>
       </c>
       <c r="K20" s="9">
-        <v>1.89</v>
+        <v>3.19</v>
       </c>
       <c r="L20" s="8">
-        <v>9.91</v>
+        <v>24</v>
       </c>
       <c r="M20" s="9">
-        <v>0.98299999999999998</v>
+        <v>1.3</v>
       </c>
       <c r="N20" s="8">
-        <v>8.25</v>
+        <v>31.8</v>
       </c>
       <c r="O20" s="8">
-        <v>29.4</v>
+        <v>52.5</v>
       </c>
       <c r="P20" s="9">
-        <v>1.89</v>
+        <v>3.19</v>
       </c>
       <c r="Q20" s="8">
-        <v>9.91</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B21" s="7">
-        <v>116.5</v>
+        <v>111</v>
       </c>
       <c r="C21" s="7">
-        <v>106.5</v>
+        <v>110</v>
       </c>
       <c r="D21" s="7">
-        <v>117.5</v>
+        <v>117</v>
       </c>
       <c r="E21" s="7">
-        <v>103.5</v>
-      </c>
-      <c r="F21" s="10">
-        <v>-10</v>
-      </c>
-      <c r="G21" s="10">
-        <v>-8.58</v>
+        <v>106</v>
+      </c>
+      <c r="F21" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="G21" s="8">
+        <v>3.29</v>
       </c>
       <c r="H21" s="9">
-        <v>0.90800000000000003</v>
+        <v>0.98299999999999998</v>
       </c>
       <c r="I21" s="8">
-        <v>1.62</v>
-      </c>
-      <c r="J21" s="10">
-        <v>-5.51</v>
+        <v>8.25</v>
+      </c>
+      <c r="J21" s="8">
+        <v>29.4</v>
       </c>
       <c r="K21" s="9">
-        <v>0.90800000000000003</v>
-      </c>
-      <c r="L21" s="10">
-        <v>-5.51</v>
+        <v>1.89</v>
+      </c>
+      <c r="L21" s="8">
+        <v>9.91</v>
       </c>
       <c r="M21" s="9">
-        <v>0.90800000000000003</v>
+        <v>0.98299999999999998</v>
       </c>
       <c r="N21" s="8">
-        <v>1.62</v>
-      </c>
-      <c r="O21" s="10">
-        <v>-5.51</v>
+        <v>8.25</v>
+      </c>
+      <c r="O21" s="8">
+        <v>29.4</v>
       </c>
       <c r="P21" s="9">
-        <v>0.90800000000000003</v>
-      </c>
-      <c r="Q21" s="10">
-        <v>-5.51</v>
+        <v>1.89</v>
+      </c>
+      <c r="Q21" s="8">
+        <v>9.91</v>
       </c>
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B22" s="7">
-        <v>115</v>
+        <v>116.5</v>
       </c>
       <c r="C22" s="7">
-        <v>116.5</v>
+        <v>106.5</v>
       </c>
       <c r="D22" s="7">
-        <v>140.5</v>
+        <v>117.5</v>
       </c>
       <c r="E22" s="7">
-        <v>112.5</v>
-      </c>
-      <c r="F22" s="8">
-        <v>2.5</v>
-      </c>
-      <c r="G22" s="8">
-        <v>2.19</v>
+        <v>103.5</v>
+      </c>
+      <c r="F22" s="10">
+        <v>-10</v>
+      </c>
+      <c r="G22" s="10">
+        <v>-8.58</v>
       </c>
       <c r="H22" s="9">
-        <v>0.89400000000000002</v>
-      </c>
-      <c r="I22" s="10">
-        <v>-55.4</v>
-      </c>
-      <c r="J22" s="8">
-        <v>16.7</v>
+        <v>0.90800000000000003</v>
+      </c>
+      <c r="I22" s="8">
+        <v>1.62</v>
+      </c>
+      <c r="J22" s="10">
+        <v>-5.51</v>
       </c>
       <c r="K22" s="9">
-        <v>13.29</v>
-      </c>
-      <c r="L22" s="8">
-        <v>41.2</v>
+        <v>0.90800000000000003</v>
+      </c>
+      <c r="L22" s="10">
+        <v>-5.51</v>
       </c>
       <c r="M22" s="9">
-        <v>0.89400000000000002</v>
-      </c>
-      <c r="N22" s="10">
-        <v>-55.4</v>
-      </c>
-      <c r="O22" s="8">
-        <v>16.7</v>
+        <v>0.90800000000000003</v>
+      </c>
+      <c r="N22" s="8">
+        <v>1.62</v>
+      </c>
+      <c r="O22" s="10">
+        <v>-5.51</v>
       </c>
       <c r="P22" s="9">
-        <v>13.29</v>
-      </c>
-      <c r="Q22" s="8">
-        <v>41.2</v>
+        <v>0.90800000000000003</v>
+      </c>
+      <c r="Q22" s="10">
+        <v>-5.51</v>
       </c>
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B23" s="7">
-        <v>106.5</v>
+        <v>115</v>
       </c>
       <c r="C23" s="7">
-        <v>114</v>
+        <v>116.5</v>
       </c>
       <c r="D23" s="7">
-        <v>118</v>
+        <v>140.5</v>
       </c>
       <c r="E23" s="7">
-        <v>105</v>
+        <v>112.5</v>
       </c>
       <c r="F23" s="8">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="G23" s="8">
-        <v>6.05</v>
+        <v>2.19</v>
       </c>
       <c r="H23" s="9">
-        <v>2</v>
-      </c>
-      <c r="I23" s="8">
-        <v>84</v>
+        <v>0.89400000000000002</v>
+      </c>
+      <c r="I23" s="10">
+        <v>-55.4</v>
       </c>
       <c r="J23" s="8">
-        <v>102.3</v>
+        <v>16.7</v>
       </c>
       <c r="K23" s="9">
-        <v>12.4</v>
+        <v>13.29</v>
       </c>
       <c r="L23" s="8">
-        <v>43.4</v>
+        <v>41.2</v>
       </c>
       <c r="M23" s="9">
-        <v>2</v>
-      </c>
-      <c r="N23" s="8">
-        <v>84</v>
+        <v>0.89400000000000002</v>
+      </c>
+      <c r="N23" s="10">
+        <v>-55.4</v>
       </c>
       <c r="O23" s="8">
-        <v>102.3</v>
+        <v>16.7</v>
       </c>
       <c r="P23" s="9">
-        <v>12.4</v>
+        <v>13.29</v>
       </c>
       <c r="Q23" s="8">
-        <v>43.4</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B24" s="7">
-        <v>125</v>
+        <v>106.5</v>
       </c>
       <c r="C24" s="7">
-        <v>107.5</v>
+        <v>114</v>
       </c>
       <c r="D24" s="7">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="E24" s="7">
-        <v>103.5</v>
+        <v>105</v>
       </c>
       <c r="F24" s="8">
-        <v>10.6</v>
+        <v>6.5</v>
       </c>
       <c r="G24" s="8">
-        <v>10.94</v>
+        <v>6.05</v>
       </c>
       <c r="H24" s="9">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="I24" s="10">
-        <v>-7.13</v>
+        <v>2</v>
+      </c>
+      <c r="I24" s="8">
+        <v>84</v>
       </c>
       <c r="J24" s="8">
-        <v>27.6</v>
+        <v>102.3</v>
       </c>
       <c r="K24" s="9">
-        <v>10.39</v>
+        <v>12.4</v>
       </c>
       <c r="L24" s="8">
-        <v>35.799999999999997</v>
+        <v>43.4</v>
       </c>
       <c r="M24" s="9">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="N24" s="10">
-        <v>-7.13</v>
+        <v>2</v>
+      </c>
+      <c r="N24" s="8">
+        <v>84</v>
       </c>
       <c r="O24" s="8">
-        <v>27.6</v>
+        <v>102.3</v>
       </c>
       <c r="P24" s="9">
-        <v>10.39</v>
+        <v>12.4</v>
       </c>
       <c r="Q24" s="8">
-        <v>35.799999999999997</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>44075</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>17</v>
+        <v>44105</v>
+      </c>
+      <c r="B25" s="7">
+        <v>125</v>
+      </c>
+      <c r="C25" s="7">
+        <v>107.5</v>
+      </c>
+      <c r="D25" s="7">
+        <v>127</v>
+      </c>
+      <c r="E25" s="7">
+        <v>103.5</v>
+      </c>
+      <c r="F25" s="8">
+        <v>10.6</v>
+      </c>
+      <c r="G25" s="8">
+        <v>10.94</v>
       </c>
       <c r="H25" s="9">
-        <v>1.17</v>
-      </c>
-      <c r="I25" s="8">
-        <v>3.76</v>
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="I25" s="10">
+        <v>-7.13</v>
       </c>
       <c r="J25" s="8">
-        <v>43.2</v>
+        <v>27.6</v>
       </c>
       <c r="K25" s="9">
-        <v>9.31</v>
+        <v>10.39</v>
       </c>
       <c r="L25" s="8">
-        <v>36.799999999999997</v>
+        <v>35.799999999999997</v>
       </c>
       <c r="M25" s="9">
-        <v>1.17</v>
-      </c>
-      <c r="N25" s="8">
-        <v>3.76</v>
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="N25" s="10">
+        <v>-7.13</v>
       </c>
       <c r="O25" s="8">
-        <v>43.2</v>
+        <v>27.6</v>
       </c>
       <c r="P25" s="9">
-        <v>9.31</v>
+        <v>10.39</v>
       </c>
       <c r="Q25" s="8">
-        <v>36.799999999999997</v>
+        <v>35.799999999999997</v>
       </c>
     </row>
     <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>44044</v>
+        <v>44075</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>17</v>
@@ -2519,39 +2519,39 @@
         <v>17</v>
       </c>
       <c r="H26" s="9">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="I26" s="10">
-        <v>-0.81</v>
+        <v>1.17</v>
+      </c>
+      <c r="I26" s="8">
+        <v>3.76</v>
       </c>
       <c r="J26" s="8">
         <v>43.2</v>
       </c>
       <c r="K26" s="9">
-        <v>8.1300000000000008</v>
+        <v>9.31</v>
       </c>
       <c r="L26" s="8">
-        <v>36</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="M26" s="9">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="N26" s="10">
-        <v>-0.81</v>
+        <v>1.17</v>
+      </c>
+      <c r="N26" s="8">
+        <v>3.76</v>
       </c>
       <c r="O26" s="8">
         <v>43.2</v>
       </c>
       <c r="P26" s="9">
-        <v>8.1300000000000008</v>
+        <v>9.31</v>
       </c>
       <c r="Q26" s="8">
-        <v>36</v>
+        <v>36.799999999999997</v>
       </c>
     </row>
     <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>17</v>
@@ -2572,39 +2572,39 @@
         <v>17</v>
       </c>
       <c r="H27" s="9">
-        <v>1.1399999999999999</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="I27" s="10">
-        <v>-5.77</v>
+        <v>-0.81</v>
       </c>
       <c r="J27" s="8">
-        <v>56.3</v>
+        <v>43.2</v>
       </c>
       <c r="K27" s="9">
-        <v>7</v>
+        <v>8.1300000000000008</v>
       </c>
       <c r="L27" s="8">
-        <v>34.9</v>
+        <v>36</v>
       </c>
       <c r="M27" s="9">
-        <v>1.1399999999999999</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="N27" s="10">
-        <v>-5.77</v>
+        <v>-0.81</v>
       </c>
       <c r="O27" s="8">
-        <v>56.3</v>
+        <v>43.2</v>
       </c>
       <c r="P27" s="9">
-        <v>7</v>
+        <v>8.1300000000000008</v>
       </c>
       <c r="Q27" s="8">
-        <v>34.9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>43983</v>
+        <v>44013</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>17</v>
@@ -2625,39 +2625,39 @@
         <v>17</v>
       </c>
       <c r="H28" s="9">
-        <v>1.21</v>
-      </c>
-      <c r="I28" s="8">
-        <v>12.8</v>
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="I28" s="10">
+        <v>-5.77</v>
       </c>
       <c r="J28" s="8">
-        <v>104.9</v>
+        <v>56.3</v>
       </c>
       <c r="K28" s="9">
-        <v>5.87</v>
+        <v>7</v>
       </c>
       <c r="L28" s="8">
-        <v>31.4</v>
+        <v>34.9</v>
       </c>
       <c r="M28" s="9">
-        <v>1.21</v>
-      </c>
-      <c r="N28" s="8">
-        <v>12.8</v>
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="N28" s="10">
+        <v>-5.77</v>
       </c>
       <c r="O28" s="8">
-        <v>104.9</v>
+        <v>56.3</v>
       </c>
       <c r="P28" s="9">
-        <v>5.87</v>
+        <v>7</v>
       </c>
       <c r="Q28" s="8">
-        <v>31.4</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>43952</v>
+        <v>43983</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>17</v>
@@ -2678,39 +2678,39 @@
         <v>17</v>
       </c>
       <c r="H29" s="9">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="I29" s="8">
-        <v>5.51</v>
+        <v>12.8</v>
       </c>
       <c r="J29" s="8">
-        <v>26.3</v>
+        <v>104.9</v>
       </c>
       <c r="K29" s="9">
-        <v>4.66</v>
+        <v>5.87</v>
       </c>
       <c r="L29" s="8">
-        <v>20.2</v>
+        <v>31.4</v>
       </c>
       <c r="M29" s="9">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="N29" s="8">
-        <v>5.51</v>
+        <v>12.8</v>
       </c>
       <c r="O29" s="8">
-        <v>26.3</v>
+        <v>104.9</v>
       </c>
       <c r="P29" s="9">
-        <v>4.66</v>
+        <v>5.87</v>
       </c>
       <c r="Q29" s="8">
-        <v>20.2</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>43922</v>
+        <v>43952</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>17</v>
@@ -2731,39 +2731,39 @@
         <v>17</v>
       </c>
       <c r="H30" s="9">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="I30" s="8">
-        <v>19.5</v>
+        <v>5.51</v>
       </c>
       <c r="J30" s="8">
-        <v>35.1</v>
+        <v>26.3</v>
       </c>
       <c r="K30" s="9">
-        <v>3.59</v>
+        <v>4.66</v>
       </c>
       <c r="L30" s="8">
-        <v>18.5</v>
+        <v>20.2</v>
       </c>
       <c r="M30" s="9">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="N30" s="8">
-        <v>19.5</v>
+        <v>5.51</v>
       </c>
       <c r="O30" s="8">
-        <v>35.1</v>
+        <v>26.3</v>
       </c>
       <c r="P30" s="9">
-        <v>3.59</v>
+        <v>4.66</v>
       </c>
       <c r="Q30" s="8">
-        <v>18.5</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>43891</v>
+        <v>43922</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>17</v>
@@ -2784,39 +2784,39 @@
         <v>17</v>
       </c>
       <c r="H31" s="9">
-        <v>0.85</v>
+        <v>1.02</v>
       </c>
       <c r="I31" s="8">
-        <v>11.9</v>
+        <v>19.5</v>
       </c>
       <c r="J31" s="8">
-        <v>4.68</v>
+        <v>35.1</v>
       </c>
       <c r="K31" s="9">
-        <v>2.57</v>
+        <v>3.59</v>
       </c>
       <c r="L31" s="8">
-        <v>13</v>
+        <v>18.5</v>
       </c>
       <c r="M31" s="9">
-        <v>0.85</v>
+        <v>1.02</v>
       </c>
       <c r="N31" s="8">
-        <v>11.9</v>
+        <v>19.5</v>
       </c>
       <c r="O31" s="8">
-        <v>4.68</v>
+        <v>35.1</v>
       </c>
       <c r="P31" s="9">
-        <v>2.57</v>
+        <v>3.59</v>
       </c>
       <c r="Q31" s="8">
-        <v>13</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>43862</v>
+        <v>43891</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>17</v>
@@ -2837,39 +2837,39 @@
         <v>17</v>
       </c>
       <c r="H32" s="9">
-        <v>0.76</v>
-      </c>
-      <c r="I32" s="10">
-        <v>-21</v>
+        <v>0.85</v>
+      </c>
+      <c r="I32" s="8">
+        <v>11.9</v>
       </c>
       <c r="J32" s="8">
-        <v>48.9</v>
+        <v>4.68</v>
       </c>
       <c r="K32" s="9">
-        <v>1.72</v>
+        <v>2.57</v>
       </c>
       <c r="L32" s="8">
-        <v>17.600000000000001</v>
+        <v>13</v>
       </c>
       <c r="M32" s="9">
-        <v>0.76</v>
-      </c>
-      <c r="N32" s="10">
-        <v>-21</v>
+        <v>0.85</v>
+      </c>
+      <c r="N32" s="8">
+        <v>11.9</v>
       </c>
       <c r="O32" s="8">
-        <v>48.9</v>
+        <v>4.68</v>
       </c>
       <c r="P32" s="9">
-        <v>1.72</v>
+        <v>2.57</v>
       </c>
       <c r="Q32" s="8">
-        <v>17.600000000000001</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>17</v>
@@ -2890,39 +2890,39 @@
         <v>17</v>
       </c>
       <c r="H33" s="9">
-        <v>0.96099999999999997</v>
-      </c>
-      <c r="I33" s="8">
-        <v>25.5</v>
+        <v>0.76</v>
+      </c>
+      <c r="I33" s="10">
+        <v>-21</v>
       </c>
       <c r="J33" s="8">
-        <v>0.8</v>
+        <v>48.9</v>
       </c>
       <c r="K33" s="9">
-        <v>0.96099999999999997</v>
+        <v>1.72</v>
       </c>
       <c r="L33" s="8">
-        <v>0.8</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="M33" s="9">
-        <v>0.96099999999999997</v>
-      </c>
-      <c r="N33" s="8">
-        <v>25.5</v>
+        <v>0.76</v>
+      </c>
+      <c r="N33" s="10">
+        <v>-21</v>
       </c>
       <c r="O33" s="8">
-        <v>0.8</v>
+        <v>48.9</v>
       </c>
       <c r="P33" s="9">
-        <v>0.96099999999999997</v>
+        <v>1.72</v>
       </c>
       <c r="Q33" s="8">
-        <v>0.8</v>
+        <v>17.600000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>43800</v>
+        <v>43831</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>17</v>
@@ -2943,39 +2943,39 @@
         <v>17</v>
       </c>
       <c r="H34" s="9">
-        <v>0.76600000000000001</v>
-      </c>
-      <c r="I34" s="10">
-        <v>-22.6</v>
+        <v>0.96099999999999997</v>
+      </c>
+      <c r="I34" s="8">
+        <v>25.5</v>
       </c>
       <c r="J34" s="8">
-        <v>2.52</v>
+        <v>0.8</v>
       </c>
       <c r="K34" s="9">
-        <v>9.41</v>
-      </c>
-      <c r="L34" s="10">
-        <v>-4.63</v>
+        <v>0.96099999999999997</v>
+      </c>
+      <c r="L34" s="8">
+        <v>0.8</v>
       </c>
       <c r="M34" s="9">
-        <v>0.76600000000000001</v>
-      </c>
-      <c r="N34" s="10">
-        <v>-22.6</v>
+        <v>0.96099999999999997</v>
+      </c>
+      <c r="N34" s="8">
+        <v>25.5</v>
       </c>
       <c r="O34" s="8">
-        <v>2.52</v>
+        <v>0.8</v>
       </c>
       <c r="P34" s="9">
-        <v>9.41</v>
-      </c>
-      <c r="Q34" s="10">
-        <v>-4.63</v>
+        <v>0.96099999999999997</v>
+      </c>
+      <c r="Q34" s="8">
+        <v>0.8</v>
       </c>
     </row>
     <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>43770</v>
+        <v>43800</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>17</v>
@@ -2996,39 +2996,39 @@
         <v>17</v>
       </c>
       <c r="H35" s="9">
-        <v>0.99</v>
-      </c>
-      <c r="I35" s="8">
-        <v>16</v>
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="I35" s="10">
+        <v>-22.6</v>
       </c>
       <c r="J35" s="8">
-        <v>0.55000000000000004</v>
+        <v>2.52</v>
       </c>
       <c r="K35" s="9">
-        <v>8.64</v>
+        <v>9.41</v>
       </c>
       <c r="L35" s="10">
-        <v>-5.21</v>
+        <v>-4.63</v>
       </c>
       <c r="M35" s="9">
-        <v>0.99</v>
-      </c>
-      <c r="N35" s="8">
-        <v>16</v>
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="N35" s="10">
+        <v>-22.6</v>
       </c>
       <c r="O35" s="8">
-        <v>0.55000000000000004</v>
+        <v>2.52</v>
       </c>
       <c r="P35" s="9">
-        <v>8.64</v>
+        <v>9.41</v>
       </c>
       <c r="Q35" s="10">
-        <v>-5.21</v>
+        <v>-4.63</v>
       </c>
     </row>
     <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>43739</v>
+        <v>43770</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>17</v>
@@ -3049,39 +3049,39 @@
         <v>17</v>
       </c>
       <c r="H36" s="9">
-        <v>0.85299999999999998</v>
+        <v>0.99</v>
       </c>
       <c r="I36" s="8">
-        <v>4.25</v>
-      </c>
-      <c r="J36" s="10">
-        <v>-20</v>
+        <v>16</v>
+      </c>
+      <c r="J36" s="8">
+        <v>0.55000000000000004</v>
       </c>
       <c r="K36" s="9">
-        <v>7.65</v>
+        <v>8.64</v>
       </c>
       <c r="L36" s="10">
-        <v>-5.91</v>
+        <v>-5.21</v>
       </c>
       <c r="M36" s="9">
-        <v>0.85299999999999998</v>
+        <v>0.99</v>
       </c>
       <c r="N36" s="8">
-        <v>4.25</v>
-      </c>
-      <c r="O36" s="10">
-        <v>-20</v>
+        <v>16</v>
+      </c>
+      <c r="O36" s="8">
+        <v>0.55000000000000004</v>
       </c>
       <c r="P36" s="9">
-        <v>7.65</v>
+        <v>8.64</v>
       </c>
       <c r="Q36" s="10">
-        <v>-5.91</v>
+        <v>-5.21</v>
       </c>
     </row>
     <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>43709</v>
+        <v>43739</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>17</v>
@@ -3102,39 +3102,39 @@
         <v>17</v>
       </c>
       <c r="H37" s="9">
-        <v>0.81799999999999995</v>
+        <v>0.85299999999999998</v>
       </c>
       <c r="I37" s="8">
-        <v>3.76</v>
+        <v>4.25</v>
       </c>
       <c r="J37" s="10">
-        <v>-8.3699999999999992</v>
+        <v>-20</v>
       </c>
       <c r="K37" s="9">
-        <v>6.8</v>
+        <v>7.65</v>
       </c>
       <c r="L37" s="10">
-        <v>-3.78</v>
+        <v>-5.91</v>
       </c>
       <c r="M37" s="9">
-        <v>0.81799999999999995</v>
+        <v>0.85299999999999998</v>
       </c>
       <c r="N37" s="8">
-        <v>3.76</v>
+        <v>4.25</v>
       </c>
       <c r="O37" s="10">
-        <v>-8.3699999999999992</v>
+        <v>-20</v>
       </c>
       <c r="P37" s="9">
-        <v>6.8</v>
+        <v>7.65</v>
       </c>
       <c r="Q37" s="10">
-        <v>-3.78</v>
+        <v>-5.91</v>
       </c>
     </row>
     <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>43678</v>
+        <v>43709</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>17</v>
@@ -3155,39 +3155,39 @@
         <v>17</v>
       </c>
       <c r="H38" s="9">
-        <v>0.78900000000000003</v>
+        <v>0.81799999999999995</v>
       </c>
       <c r="I38" s="8">
-        <v>8.23</v>
+        <v>3.76</v>
       </c>
       <c r="J38" s="10">
-        <v>-11.8</v>
+        <v>-8.3699999999999992</v>
       </c>
       <c r="K38" s="9">
-        <v>5.98</v>
+        <v>6.8</v>
       </c>
       <c r="L38" s="10">
-        <v>-3.11</v>
+        <v>-3.78</v>
       </c>
       <c r="M38" s="9">
-        <v>0.78900000000000003</v>
+        <v>0.81799999999999995</v>
       </c>
       <c r="N38" s="8">
-        <v>8.23</v>
+        <v>3.76</v>
       </c>
       <c r="O38" s="10">
-        <v>-11.8</v>
+        <v>-8.3699999999999992</v>
       </c>
       <c r="P38" s="9">
-        <v>5.98</v>
+        <v>6.8</v>
       </c>
       <c r="Q38" s="10">
-        <v>-3.11</v>
+        <v>-3.78</v>
       </c>
     </row>
     <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>43647</v>
+        <v>43678</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>17</v>
@@ -3208,39 +3208,39 @@
         <v>17</v>
       </c>
       <c r="H39" s="9">
-        <v>0.72899999999999998</v>
+        <v>0.78900000000000003</v>
       </c>
       <c r="I39" s="8">
-        <v>23.5</v>
+        <v>8.23</v>
       </c>
       <c r="J39" s="10">
-        <v>-7.96</v>
+        <v>-11.8</v>
       </c>
       <c r="K39" s="9">
-        <v>5.19</v>
+        <v>5.98</v>
       </c>
       <c r="L39" s="10">
-        <v>-1.66</v>
+        <v>-3.11</v>
       </c>
       <c r="M39" s="9">
-        <v>0.72899999999999998</v>
+        <v>0.78900000000000003</v>
       </c>
       <c r="N39" s="8">
-        <v>23.5</v>
+        <v>8.23</v>
       </c>
       <c r="O39" s="10">
-        <v>-7.96</v>
+        <v>-11.8</v>
       </c>
       <c r="P39" s="9">
-        <v>5.19</v>
+        <v>5.98</v>
       </c>
       <c r="Q39" s="10">
-        <v>-1.66</v>
+        <v>-3.11</v>
       </c>
     </row>
     <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>43617</v>
+        <v>43647</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>17</v>
@@ -3261,39 +3261,39 @@
         <v>17</v>
       </c>
       <c r="H40" s="9">
-        <v>0.59</v>
-      </c>
-      <c r="I40" s="10">
-        <v>-30.5</v>
+        <v>0.72899999999999998</v>
+      </c>
+      <c r="I40" s="8">
+        <v>23.5</v>
       </c>
       <c r="J40" s="10">
-        <v>-12.4</v>
+        <v>-7.96</v>
       </c>
       <c r="K40" s="9">
-        <v>4.47</v>
+        <v>5.19</v>
       </c>
       <c r="L40" s="10">
-        <v>-0.54</v>
+        <v>-1.66</v>
       </c>
       <c r="M40" s="9">
-        <v>0.59</v>
-      </c>
-      <c r="N40" s="10">
-        <v>-30.5</v>
+        <v>0.72899999999999998</v>
+      </c>
+      <c r="N40" s="8">
+        <v>23.5</v>
       </c>
       <c r="O40" s="10">
-        <v>-12.4</v>
+        <v>-7.96</v>
       </c>
       <c r="P40" s="9">
-        <v>4.47</v>
+        <v>5.19</v>
       </c>
       <c r="Q40" s="10">
-        <v>-0.54</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>43586</v>
+        <v>43617</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>17</v>
@@ -3314,39 +3314,39 @@
         <v>17</v>
       </c>
       <c r="H41" s="9">
-        <v>0.84899999999999998</v>
-      </c>
-      <c r="I41" s="8">
-        <v>12.9</v>
+        <v>0.59</v>
+      </c>
+      <c r="I41" s="10">
+        <v>-30.5</v>
       </c>
       <c r="J41" s="10">
-        <v>-10.9</v>
+        <v>-12.4</v>
       </c>
       <c r="K41" s="9">
-        <v>3.88</v>
-      </c>
-      <c r="L41" s="8">
-        <v>1.55</v>
+        <v>4.47</v>
+      </c>
+      <c r="L41" s="10">
+        <v>-0.54</v>
       </c>
       <c r="M41" s="9">
-        <v>0.84899999999999998</v>
-      </c>
-      <c r="N41" s="8">
-        <v>12.9</v>
+        <v>0.59</v>
+      </c>
+      <c r="N41" s="10">
+        <v>-30.5</v>
       </c>
       <c r="O41" s="10">
-        <v>-10.9</v>
+        <v>-12.4</v>
       </c>
       <c r="P41" s="9">
-        <v>3.88</v>
-      </c>
-      <c r="Q41" s="8">
-        <v>1.55</v>
+        <v>4.47</v>
+      </c>
+      <c r="Q41" s="10">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
-        <v>43556</v>
+        <v>43586</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>17</v>
@@ -3367,39 +3367,39 @@
         <v>17</v>
       </c>
       <c r="H42" s="9">
-        <v>0.752</v>
-      </c>
-      <c r="I42" s="10">
-        <v>-7.38</v>
+        <v>0.84899999999999998</v>
+      </c>
+      <c r="I42" s="8">
+        <v>12.9</v>
       </c>
       <c r="J42" s="10">
-        <v>-6</v>
+        <v>-10.9</v>
       </c>
       <c r="K42" s="9">
-        <v>3.03</v>
+        <v>3.88</v>
       </c>
       <c r="L42" s="8">
-        <v>5.7</v>
+        <v>1.55</v>
       </c>
       <c r="M42" s="9">
-        <v>0.752</v>
-      </c>
-      <c r="N42" s="10">
-        <v>-7.38</v>
+        <v>0.84899999999999998</v>
+      </c>
+      <c r="N42" s="8">
+        <v>12.9</v>
       </c>
       <c r="O42" s="10">
-        <v>-6</v>
+        <v>-10.9</v>
       </c>
       <c r="P42" s="9">
-        <v>3.03</v>
+        <v>3.88</v>
       </c>
       <c r="Q42" s="8">
-        <v>5.7</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
-        <v>43525</v>
+        <v>43556</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>17</v>
@@ -3420,39 +3420,39 @@
         <v>17</v>
       </c>
       <c r="H43" s="9">
-        <v>0.81200000000000006</v>
-      </c>
-      <c r="I43" s="8">
-        <v>59.1</v>
-      </c>
-      <c r="J43" s="8">
-        <v>3.75</v>
+        <v>0.752</v>
+      </c>
+      <c r="I43" s="10">
+        <v>-7.38</v>
+      </c>
+      <c r="J43" s="10">
+        <v>-6</v>
       </c>
       <c r="K43" s="9">
-        <v>2.2799999999999998</v>
+        <v>3.03</v>
       </c>
       <c r="L43" s="8">
-        <v>10.199999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="M43" s="9">
-        <v>0.81200000000000006</v>
-      </c>
-      <c r="N43" s="8">
-        <v>59.1</v>
-      </c>
-      <c r="O43" s="8">
-        <v>3.75</v>
+        <v>0.752</v>
+      </c>
+      <c r="N43" s="10">
+        <v>-7.38</v>
+      </c>
+      <c r="O43" s="10">
+        <v>-6</v>
       </c>
       <c r="P43" s="9">
-        <v>2.2799999999999998</v>
+        <v>3.03</v>
       </c>
       <c r="Q43" s="8">
-        <v>10.199999999999999</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
-        <v>43497</v>
+        <v>43525</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>17</v>
@@ -3473,39 +3473,39 @@
         <v>17</v>
       </c>
       <c r="H44" s="9">
-        <v>0.51</v>
-      </c>
-      <c r="I44" s="10">
-        <v>-46.5</v>
-      </c>
-      <c r="J44" s="10">
-        <v>-2.1800000000000002</v>
+        <v>0.81200000000000006</v>
+      </c>
+      <c r="I44" s="8">
+        <v>59.1</v>
+      </c>
+      <c r="J44" s="8">
+        <v>3.75</v>
       </c>
       <c r="K44" s="9">
-        <v>1.46</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="L44" s="8">
-        <v>14.2</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="M44" s="9">
-        <v>0.51</v>
-      </c>
-      <c r="N44" s="10">
-        <v>-46.5</v>
-      </c>
-      <c r="O44" s="10">
-        <v>-2.1800000000000002</v>
+        <v>0.81200000000000006</v>
+      </c>
+      <c r="N44" s="8">
+        <v>59.1</v>
+      </c>
+      <c r="O44" s="8">
+        <v>3.75</v>
       </c>
       <c r="P44" s="9">
-        <v>1.46</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="Q44" s="8">
-        <v>14.2</v>
+        <v>10.199999999999999</v>
       </c>
     </row>
     <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
-        <v>43466</v>
+        <v>43497</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>17</v>
@@ -3526,39 +3526,39 @@
         <v>17</v>
       </c>
       <c r="H45" s="9">
-        <v>0.95299999999999996</v>
-      </c>
-      <c r="I45" s="8">
-        <v>27.7</v>
-      </c>
-      <c r="J45" s="8">
-        <v>25.4</v>
+        <v>0.51</v>
+      </c>
+      <c r="I45" s="10">
+        <v>-46.5</v>
+      </c>
+      <c r="J45" s="10">
+        <v>-2.1800000000000002</v>
       </c>
       <c r="K45" s="9">
-        <v>0.95299999999999996</v>
+        <v>1.46</v>
       </c>
       <c r="L45" s="8">
-        <v>25.4</v>
+        <v>14.2</v>
       </c>
       <c r="M45" s="9">
-        <v>0.95299999999999996</v>
-      </c>
-      <c r="N45" s="8">
-        <v>27.7</v>
-      </c>
-      <c r="O45" s="8">
-        <v>25.4</v>
+        <v>0.51</v>
+      </c>
+      <c r="N45" s="10">
+        <v>-46.5</v>
+      </c>
+      <c r="O45" s="10">
+        <v>-2.1800000000000002</v>
       </c>
       <c r="P45" s="9">
-        <v>0.95299999999999996</v>
+        <v>1.46</v>
       </c>
       <c r="Q45" s="8">
-        <v>25.4</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
-        <v>43435</v>
+        <v>43466</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>17</v>
@@ -3579,39 +3579,39 @@
         <v>17</v>
       </c>
       <c r="H46" s="9">
-        <v>0.747</v>
-      </c>
-      <c r="I46" s="10">
-        <v>-24.1</v>
+        <v>0.95299999999999996</v>
+      </c>
+      <c r="I46" s="8">
+        <v>27.7</v>
       </c>
       <c r="J46" s="8">
-        <v>10.5</v>
+        <v>25.4</v>
       </c>
       <c r="K46" s="9">
-        <v>9.8699999999999992</v>
+        <v>0.95299999999999996</v>
       </c>
       <c r="L46" s="8">
-        <v>11.4</v>
+        <v>25.4</v>
       </c>
       <c r="M46" s="9">
-        <v>0.747</v>
-      </c>
-      <c r="N46" s="10">
-        <v>-24.1</v>
+        <v>0.95299999999999996</v>
+      </c>
+      <c r="N46" s="8">
+        <v>27.7</v>
       </c>
       <c r="O46" s="8">
-        <v>10.5</v>
+        <v>25.4</v>
       </c>
       <c r="P46" s="9">
-        <v>9.8699999999999992</v>
+        <v>0.95299999999999996</v>
       </c>
       <c r="Q46" s="8">
-        <v>11.4</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
-        <v>43405</v>
+        <v>43435</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>17</v>
@@ -3632,39 +3632,39 @@
         <v>17</v>
       </c>
       <c r="H47" s="9">
-        <v>0.98399999999999999</v>
+        <v>0.747</v>
       </c>
       <c r="I47" s="10">
-        <v>-7.75</v>
-      </c>
-      <c r="J47" s="10">
-        <v>-0.02</v>
+        <v>-24.1</v>
+      </c>
+      <c r="J47" s="8">
+        <v>10.5</v>
       </c>
       <c r="K47" s="9">
-        <v>9.1199999999999992</v>
+        <v>9.8699999999999992</v>
       </c>
       <c r="L47" s="8">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="M47" s="9">
-        <v>0.98399999999999999</v>
+        <v>0.747</v>
       </c>
       <c r="N47" s="10">
-        <v>-7.75</v>
-      </c>
-      <c r="O47" s="10">
-        <v>-0.02</v>
+        <v>-24.1</v>
+      </c>
+      <c r="O47" s="8">
+        <v>10.5</v>
       </c>
       <c r="P47" s="9">
-        <v>9.1199999999999992</v>
+        <v>9.8699999999999992</v>
       </c>
       <c r="Q47" s="8">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
-        <v>43374</v>
+        <v>43405</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>17</v>
@@ -3685,39 +3685,39 @@
         <v>17</v>
       </c>
       <c r="H48" s="9">
-        <v>1.07</v>
-      </c>
-      <c r="I48" s="8">
-        <v>19.5</v>
-      </c>
-      <c r="J48" s="8">
-        <v>18.100000000000001</v>
+        <v>0.98399999999999999</v>
+      </c>
+      <c r="I48" s="10">
+        <v>-7.75</v>
+      </c>
+      <c r="J48" s="10">
+        <v>-0.02</v>
       </c>
       <c r="K48" s="9">
-        <v>8.14</v>
+        <v>9.1199999999999992</v>
       </c>
       <c r="L48" s="8">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="M48" s="9">
-        <v>1.07</v>
-      </c>
-      <c r="N48" s="8">
-        <v>19.5</v>
-      </c>
-      <c r="O48" s="8">
-        <v>18.100000000000001</v>
+        <v>0.98399999999999999</v>
+      </c>
+      <c r="N48" s="10">
+        <v>-7.75</v>
+      </c>
+      <c r="O48" s="10">
+        <v>-0.02</v>
       </c>
       <c r="P48" s="9">
-        <v>8.14</v>
+        <v>9.1199999999999992</v>
       </c>
       <c r="Q48" s="8">
-        <v>13</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
-        <v>43344</v>
+        <v>43374</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>17</v>
@@ -3738,86 +3738,139 @@
         <v>17</v>
       </c>
       <c r="H49" s="9">
-        <v>0.89300000000000002</v>
-      </c>
-      <c r="I49" s="10">
-        <v>-0.06</v>
+        <v>1.07</v>
+      </c>
+      <c r="I49" s="8">
+        <v>19.5</v>
       </c>
       <c r="J49" s="8">
-        <v>14.3</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="K49" s="9">
-        <v>7.07</v>
+        <v>8.14</v>
       </c>
       <c r="L49" s="8">
-        <v>12.3</v>
+        <v>13</v>
       </c>
       <c r="M49" s="9">
-        <v>0.89300000000000002</v>
-      </c>
-      <c r="N49" s="10">
-        <v>-0.06</v>
+        <v>1.07</v>
+      </c>
+      <c r="N49" s="8">
+        <v>19.5</v>
       </c>
       <c r="O49" s="8">
-        <v>14.3</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="P49" s="9">
-        <v>7.07</v>
+        <v>8.14</v>
       </c>
       <c r="Q49" s="8">
-        <v>12.3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
+        <v>43344</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H50" s="9">
+        <v>0.89300000000000002</v>
+      </c>
+      <c r="I50" s="10">
+        <v>-0.06</v>
+      </c>
+      <c r="J50" s="8">
+        <v>14.3</v>
+      </c>
+      <c r="K50" s="9">
+        <v>7.07</v>
+      </c>
+      <c r="L50" s="8">
+        <v>12.3</v>
+      </c>
+      <c r="M50" s="9">
+        <v>0.89300000000000002</v>
+      </c>
+      <c r="N50" s="10">
+        <v>-0.06</v>
+      </c>
+      <c r="O50" s="8">
+        <v>14.3</v>
+      </c>
+      <c r="P50" s="9">
+        <v>7.07</v>
+      </c>
+      <c r="Q50" s="8">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A51" s="6">
         <v>43313</v>
       </c>
-      <c r="B50" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G50" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H50" s="9">
+      <c r="B51" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H51" s="9">
         <v>0.89400000000000002</v>
       </c>
-      <c r="I50" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J50" s="8">
+      <c r="I51" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J51" s="8">
         <v>0.33</v>
       </c>
-      <c r="K50" s="9">
+      <c r="K51" s="9">
         <v>6.18</v>
       </c>
-      <c r="L50" s="8">
+      <c r="L51" s="8">
         <v>12</v>
       </c>
-      <c r="M50" s="9">
+      <c r="M51" s="9">
         <v>0.89400000000000002</v>
       </c>
-      <c r="N50" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O50" s="8">
+      <c r="N51" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O51" s="8">
         <v>0.33</v>
       </c>
-      <c r="P50" s="9">
+      <c r="P51" s="9">
         <v>6.18</v>
       </c>
-      <c r="Q50" s="8">
+      <c r="Q51" s="8">
         <v>12</v>
       </c>
     </row>
